--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/135.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/135.xlsx
@@ -426,13 +426,13 @@
         <v>2.851578796659628</v>
       </c>
       <c r="E2">
-        <v>-15.86691461406988</v>
+        <v>-16.45853126086906</v>
       </c>
       <c r="F2">
-        <v>-1.635597501829284</v>
+        <v>-2.678247812752368</v>
       </c>
       <c r="G2">
-        <v>-13.16319354284732</v>
+        <v>-13.39371837412573</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.47785326604808</v>
       </c>
       <c r="E3">
-        <v>-16.61168092847211</v>
+        <v>-18.2465136554757</v>
       </c>
       <c r="F3">
-        <v>-1.974597749383551</v>
+        <v>-2.614384827833541</v>
       </c>
       <c r="G3">
-        <v>-12.60934104768248</v>
+        <v>-12.90398837686323</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.070503183068939</v>
       </c>
       <c r="E4">
-        <v>-17.69604287327159</v>
+        <v>-18.98414890603319</v>
       </c>
       <c r="F4">
-        <v>-3.208960441806136</v>
+        <v>-2.754645653210359</v>
       </c>
       <c r="G4">
-        <v>-12.85540764151179</v>
+        <v>-12.91399666625326</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.560121401092622</v>
       </c>
       <c r="E5">
-        <v>-17.93779299806722</v>
+        <v>-17.49653090764948</v>
       </c>
       <c r="F5">
-        <v>-2.616623076555905</v>
+        <v>-2.690753675432433</v>
       </c>
       <c r="G5">
-        <v>-12.11608001836049</v>
+        <v>-12.67853491695305</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.960753173804967</v>
       </c>
       <c r="E6">
-        <v>-22.09421060203853</v>
+        <v>-20.11575778286393</v>
       </c>
       <c r="F6">
-        <v>-1.796188120005607</v>
+        <v>-2.681885174018061</v>
       </c>
       <c r="G6">
-        <v>-11.55320609526105</v>
+        <v>-13.84252103380565</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>5.262298521543121</v>
       </c>
       <c r="E7">
-        <v>-20.96304196560822</v>
+        <v>-20.67965174406987</v>
       </c>
       <c r="F7">
-        <v>-2.27106050243666</v>
+        <v>-2.791584212435994</v>
       </c>
       <c r="G7">
-        <v>-11.62870491271916</v>
+        <v>-13.52224924646313</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>5.472396218580002</v>
       </c>
       <c r="E8">
-        <v>-21.51133646507811</v>
+        <v>-21.88560310361504</v>
       </c>
       <c r="F8">
-        <v>-1.892378142818686</v>
+        <v>-2.096478758827053</v>
       </c>
       <c r="G8">
-        <v>-13.00103758554868</v>
+        <v>-13.31420553685879</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>5.59907700048116</v>
       </c>
       <c r="E9">
-        <v>-22.82590676040152</v>
+        <v>-23.71983565953497</v>
       </c>
       <c r="F9">
-        <v>-2.021221580282718</v>
+        <v>-2.251804273791183</v>
       </c>
       <c r="G9">
-        <v>-11.80723676546556</v>
+        <v>-13.07543597416164</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>5.654924190059345</v>
       </c>
       <c r="E10">
-        <v>-24.57720383937594</v>
+        <v>-23.34346334285635</v>
       </c>
       <c r="F10">
-        <v>-2.477711661678248</v>
+        <v>-2.120828618632345</v>
       </c>
       <c r="G10">
-        <v>-11.6635374670538</v>
+        <v>-13.90040254676293</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.6505282518803</v>
       </c>
       <c r="E11">
-        <v>-25.50128920593897</v>
+        <v>-24.66035943652166</v>
       </c>
       <c r="F11">
-        <v>-1.670615077047827</v>
+        <v>-1.885423998472184</v>
       </c>
       <c r="G11">
-        <v>-10.35225052962599</v>
+        <v>-12.58005893634855</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.601718292859961</v>
       </c>
       <c r="E12">
-        <v>-25.20513201278809</v>
+        <v>-24.37305688991532</v>
       </c>
       <c r="F12">
-        <v>-1.121506893080091</v>
+        <v>-1.825234822984772</v>
       </c>
       <c r="G12">
-        <v>-10.43731250452134</v>
+        <v>-12.82330200990257</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.516928435296383</v>
       </c>
       <c r="E13">
-        <v>-28.53895627534121</v>
+        <v>-26.38937868994971</v>
       </c>
       <c r="F13">
-        <v>-1.00346122471155</v>
+        <v>-1.450468984447234</v>
       </c>
       <c r="G13">
-        <v>-10.60020991328386</v>
+        <v>-12.29819250731359</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.406104277756059</v>
       </c>
       <c r="E14">
-        <v>-25.01527211028488</v>
+        <v>-26.51644203722151</v>
       </c>
       <c r="F14">
-        <v>-1.620602395103807</v>
+        <v>-1.625427635225114</v>
       </c>
       <c r="G14">
-        <v>-8.741127408142589</v>
+        <v>-12.10913804849272</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>5.276125775687412</v>
       </c>
       <c r="E15">
-        <v>-25.90040450783234</v>
+        <v>-28.61179737216172</v>
       </c>
       <c r="F15">
-        <v>-0.9917282288182983</v>
+        <v>-0.8437105710816658</v>
       </c>
       <c r="G15">
-        <v>-9.723444862622578</v>
+        <v>-11.640827905228</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.125914434760416</v>
       </c>
       <c r="E16">
-        <v>-29.83643610606295</v>
+        <v>-29.2138946477391</v>
       </c>
       <c r="F16">
-        <v>-1.402005349546449</v>
+        <v>-0.7498863655709826</v>
       </c>
       <c r="G16">
-        <v>-9.054529021093602</v>
+        <v>-11.17749123040935</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.955800575408015</v>
       </c>
       <c r="E17">
-        <v>-29.68496848904645</v>
+        <v>-31.02064125111131</v>
       </c>
       <c r="F17">
-        <v>-0.5167092253569497</v>
+        <v>-0.7622323533423064</v>
       </c>
       <c r="G17">
-        <v>-7.083760167716802</v>
+        <v>-10.504073159833</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.759923463762045</v>
       </c>
       <c r="E18">
-        <v>-31.28019411625081</v>
+        <v>-31.83111552188365</v>
       </c>
       <c r="F18">
-        <v>-1.3333428038958</v>
+        <v>-0.2113945382375248</v>
       </c>
       <c r="G18">
-        <v>-7.508820716085139</v>
+        <v>-9.606602293819599</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.527596346617159</v>
       </c>
       <c r="E19">
-        <v>-34.01169059999802</v>
+        <v>-33.07410522002364</v>
       </c>
       <c r="F19">
-        <v>-0.4516003758643115</v>
+        <v>-0.241488297613828</v>
       </c>
       <c r="G19">
-        <v>-6.910907989828374</v>
+        <v>-9.579301737630328</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.255166930200896</v>
       </c>
       <c r="E20">
-        <v>-36.06876163294596</v>
+        <v>-33.37445715661259</v>
       </c>
       <c r="F20">
-        <v>0.06650367295144495</v>
+        <v>0.3484492872704931</v>
       </c>
       <c r="G20">
-        <v>-6.406647893544025</v>
+        <v>-8.177403687678749</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.935862523167245</v>
       </c>
       <c r="E21">
-        <v>-35.29330931667023</v>
+        <v>-35.14975356722753</v>
       </c>
       <c r="F21">
-        <v>-0.1477568692522584</v>
+        <v>0.8265456756332418</v>
       </c>
       <c r="G21">
-        <v>-6.607685670038112</v>
+        <v>-8.632338986403195</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.565872374109927</v>
       </c>
       <c r="E22">
-        <v>-37.32656583588161</v>
+        <v>-36.17100538934059</v>
       </c>
       <c r="F22">
-        <v>1.202980674487421</v>
+        <v>1.112887435758947</v>
       </c>
       <c r="G22">
-        <v>-5.821052660268133</v>
+        <v>-7.78229490663196</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.153498950027902</v>
       </c>
       <c r="E23">
-        <v>-36.57864723408383</v>
+        <v>-36.04024153077836</v>
       </c>
       <c r="F23">
-        <v>0.8137059808898495</v>
+        <v>1.491247560457232</v>
       </c>
       <c r="G23">
-        <v>-5.181976324043285</v>
+        <v>-7.525009943294632</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.706110505281746</v>
       </c>
       <c r="E24">
-        <v>-38.32402391031471</v>
+        <v>-37.78737293879399</v>
       </c>
       <c r="F24">
-        <v>1.299740614073626</v>
+        <v>1.738376064469214</v>
       </c>
       <c r="G24">
-        <v>-5.131881356829004</v>
+        <v>-6.675732117060889</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.23523928663926</v>
       </c>
       <c r="E25">
-        <v>-37.40597315980666</v>
+        <v>-38.17806760472627</v>
       </c>
       <c r="F25">
-        <v>1.477773336283295</v>
+        <v>1.35696257752421</v>
       </c>
       <c r="G25">
-        <v>-6.139868957501114</v>
+        <v>-6.267610079599696</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.760957219977381</v>
       </c>
       <c r="E26">
-        <v>-37.70824595663335</v>
+        <v>-37.5920806358779</v>
       </c>
       <c r="F26">
-        <v>1.428381101523972</v>
+        <v>2.377019167535938</v>
       </c>
       <c r="G26">
-        <v>-3.725890964730854</v>
+        <v>-6.735526000431157</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.297848724880213</v>
       </c>
       <c r="E27">
-        <v>-40.81102707318626</v>
+        <v>-37.59026152931762</v>
       </c>
       <c r="F27">
-        <v>1.596668909607108</v>
+        <v>1.819126975628916</v>
       </c>
       <c r="G27">
-        <v>-5.717032763524406</v>
+        <v>-6.949831580937282</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.860154076439902</v>
       </c>
       <c r="E28">
-        <v>-39.96984811108946</v>
+        <v>-39.71485339537896</v>
       </c>
       <c r="F28">
-        <v>0.8418787562590606</v>
+        <v>1.634089578661173</v>
       </c>
       <c r="G28">
-        <v>-6.136527204424489</v>
+        <v>-7.035197707577504</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.4643618913088933</v>
       </c>
       <c r="E29">
-        <v>-38.7238847136409</v>
+        <v>-38.75463301368426</v>
       </c>
       <c r="F29">
-        <v>1.501665108914839</v>
+        <v>1.907749033850018</v>
       </c>
       <c r="G29">
-        <v>-4.904535107090267</v>
+        <v>-6.850665058388435</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.1183112530699204</v>
       </c>
       <c r="E30">
-        <v>-40.60728506182981</v>
+        <v>-39.53402049769026</v>
       </c>
       <c r="F30">
-        <v>1.214693789563006</v>
+        <v>1.502182010174186</v>
       </c>
       <c r="G30">
-        <v>-5.050494004945637</v>
+        <v>-6.369810287363417</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.1728711392636028</v>
       </c>
       <c r="E31">
-        <v>-41.44956254832202</v>
+        <v>-38.19033826758547</v>
       </c>
       <c r="F31">
-        <v>0.5373278238850168</v>
+        <v>1.35934164870505</v>
       </c>
       <c r="G31">
-        <v>-5.037623034111449</v>
+        <v>-6.230365197262874</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.4030731500823726</v>
       </c>
       <c r="E32">
-        <v>-38.90781175376659</v>
+        <v>-38.98546019269558</v>
       </c>
       <c r="F32">
-        <v>0.8524520377883935</v>
+        <v>1.104211115582025</v>
       </c>
       <c r="G32">
-        <v>-4.473733531366073</v>
+        <v>-6.731863125769824</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.5719066699639617</v>
       </c>
       <c r="E33">
-        <v>-37.29834061171807</v>
+        <v>-39.06666585712429</v>
       </c>
       <c r="F33">
-        <v>0.85168165610379</v>
+        <v>0.8102931071903154</v>
       </c>
       <c r="G33">
-        <v>-3.568799851938977</v>
+        <v>-6.001222755245451</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.6799034051693273</v>
       </c>
       <c r="E34">
-        <v>-38.89489734315204</v>
+        <v>-37.28570446626228</v>
       </c>
       <c r="F34">
-        <v>0.3029172446082155</v>
+        <v>0.8026737838193656</v>
       </c>
       <c r="G34">
-        <v>-3.879846573268805</v>
+        <v>-6.204667638252546</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.7269126470719796</v>
       </c>
       <c r="E35">
-        <v>-38.01409466841071</v>
+        <v>-36.50319169073435</v>
       </c>
       <c r="F35">
-        <v>0.5799282743087869</v>
+        <v>0.6264212231583119</v>
       </c>
       <c r="G35">
-        <v>-3.420261538427587</v>
+        <v>-5.324026937245759</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.7140906497888621</v>
       </c>
       <c r="E36">
-        <v>-37.6555956966685</v>
+        <v>-36.89918170110579</v>
       </c>
       <c r="F36">
-        <v>0.1220266548588874</v>
+        <v>0.3379762381968989</v>
       </c>
       <c r="G36">
-        <v>-3.472546920353812</v>
+        <v>-5.920281840687166</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6428221365882124</v>
       </c>
       <c r="E37">
-        <v>-36.63343224466965</v>
+        <v>-36.2010331072191</v>
       </c>
       <c r="F37">
-        <v>-0.2744150735077056</v>
+        <v>0.08003091263916089</v>
       </c>
       <c r="G37">
-        <v>-3.918428156836277</v>
+        <v>-5.933439993426378</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.5135201817156334</v>
       </c>
       <c r="E38">
-        <v>-36.52148243340889</v>
+        <v>-35.34381028977449</v>
       </c>
       <c r="F38">
-        <v>0.2526113206036043</v>
+        <v>-0.06477019447240109</v>
       </c>
       <c r="G38">
-        <v>-3.034205514250483</v>
+        <v>-4.607750883461691</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.3230991933593605</v>
       </c>
       <c r="E39">
-        <v>-37.78232263382299</v>
+        <v>-35.2767857654144</v>
       </c>
       <c r="F39">
-        <v>-0.5026244944071497</v>
+        <v>-0.1674720134388866</v>
       </c>
       <c r="G39">
-        <v>-3.086216767994642</v>
+        <v>-4.489617301458406</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.06947223962863477</v>
       </c>
       <c r="E40">
-        <v>-35.70910599184978</v>
+        <v>-33.86709239451279</v>
       </c>
       <c r="F40">
-        <v>0.2715544263708234</v>
+        <v>-0.4683126882157915</v>
       </c>
       <c r="G40">
-        <v>-0.9475156849113667</v>
+        <v>-4.688375897924452</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.2496038485006873</v>
       </c>
       <c r="E41">
-        <v>-35.07189331452098</v>
+        <v>-35.3265163178179</v>
       </c>
       <c r="F41">
-        <v>-0.5263646758039808</v>
+        <v>-0.3282150512173251</v>
       </c>
       <c r="G41">
-        <v>-0.8544974658745915</v>
+        <v>-4.35349307847776</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.6409281709202584</v>
       </c>
       <c r="E42">
-        <v>-33.81272893487645</v>
+        <v>-33.26845474396899</v>
       </c>
       <c r="F42">
-        <v>-0.5578741150716684</v>
+        <v>-0.4979906071558893</v>
       </c>
       <c r="G42">
-        <v>-2.048419685581199</v>
+        <v>-4.112255056769709</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.105917539442494</v>
       </c>
       <c r="E43">
-        <v>-33.66703635820712</v>
+        <v>-33.1880880282279</v>
       </c>
       <c r="F43">
-        <v>-0.4601930309335507</v>
+        <v>-0.8850137981526519</v>
       </c>
       <c r="G43">
-        <v>-1.226050803848061</v>
+        <v>-4.096504434651523</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.643575685823884</v>
       </c>
       <c r="E44">
-        <v>-33.83341815709108</v>
+        <v>-32.29510398467085</v>
       </c>
       <c r="F44">
-        <v>-0.6248293955051468</v>
+        <v>-0.8729362014198352</v>
       </c>
       <c r="G44">
-        <v>-0.7870097181943131</v>
+        <v>-3.414912122760395</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.257986937820175</v>
       </c>
       <c r="E45">
-        <v>-33.89455965760954</v>
+        <v>-31.70998711359503</v>
       </c>
       <c r="F45">
-        <v>-0.1671158154556828</v>
+        <v>-0.5167796365861878</v>
       </c>
       <c r="G45">
-        <v>-1.88597654637754</v>
+        <v>-3.452042132335209</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.942475373230578</v>
       </c>
       <c r="E46">
-        <v>-33.85666575748181</v>
+        <v>-31.46768668829887</v>
       </c>
       <c r="F46">
-        <v>0.5132372430768015</v>
+        <v>-0.6568855572586821</v>
       </c>
       <c r="G46">
-        <v>-1.364660455679447</v>
+        <v>-3.664410540354727</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.687321707163739</v>
       </c>
       <c r="E47">
-        <v>-32.71371653712863</v>
+        <v>-30.59227072864585</v>
       </c>
       <c r="F47">
-        <v>-1.078952831230878</v>
+        <v>-0.9747723764503952</v>
       </c>
       <c r="G47">
-        <v>-1.567000993724501</v>
+        <v>-3.284327899802091</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.486616722399788</v>
       </c>
       <c r="E48">
-        <v>-31.42317879913634</v>
+        <v>-30.20070596494101</v>
       </c>
       <c r="F48">
-        <v>-0.6161630157370585</v>
+        <v>-0.6630113342023845</v>
       </c>
       <c r="G48">
-        <v>-1.994776716467595</v>
+        <v>-3.51022779703735</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.320584481166571</v>
       </c>
       <c r="E49">
-        <v>-30.41055527355062</v>
+        <v>-29.40694629314544</v>
       </c>
       <c r="F49">
-        <v>-0.08817820054070953</v>
+        <v>-1.077654779510691</v>
       </c>
       <c r="G49">
-        <v>-1.863448431300823</v>
+        <v>-3.91123555548776</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>6.166356536288787</v>
       </c>
       <c r="E50">
-        <v>-28.65714421001186</v>
+        <v>-29.0377361893965</v>
       </c>
       <c r="F50">
-        <v>-0.06991849788080003</v>
+        <v>-0.8021116168478802</v>
       </c>
       <c r="G50">
-        <v>-2.091410816763062</v>
+        <v>-4.052247092342971</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>7.005412541871386</v>
       </c>
       <c r="E51">
-        <v>-28.4549824955645</v>
+        <v>-27.59089857301128</v>
       </c>
       <c r="F51">
-        <v>-0.2249938458892843</v>
+        <v>-0.8849624393736784</v>
       </c>
       <c r="G51">
-        <v>-2.65094298678587</v>
+        <v>-3.981884914867877</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>7.808980205922773</v>
       </c>
       <c r="E52">
-        <v>-28.22743843010546</v>
+        <v>-27.10751461333713</v>
       </c>
       <c r="F52">
-        <v>-1.140409408844573</v>
+        <v>-0.8307275687775891</v>
       </c>
       <c r="G52">
-        <v>-3.221134826974194</v>
+        <v>-4.243797422992952</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>8.551192251232926</v>
       </c>
       <c r="E53">
-        <v>-27.10360644148047</v>
+        <v>-27.75067676588876</v>
       </c>
       <c r="F53">
-        <v>-1.069924454907766</v>
+        <v>-0.8288869364085687</v>
       </c>
       <c r="G53">
-        <v>-2.314650365259977</v>
+        <v>-4.243601617148619</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>9.211865142575617</v>
       </c>
       <c r="E54">
-        <v>-26.4445125702868</v>
+        <v>-25.35246303132506</v>
       </c>
       <c r="F54">
-        <v>-1.082245591657006</v>
+        <v>-0.7916915832880652</v>
       </c>
       <c r="G54">
-        <v>-1.995711363031213</v>
+        <v>-4.54328115652874</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>9.765329075738149</v>
       </c>
       <c r="E55">
-        <v>-26.74547918215183</v>
+        <v>-25.08477610180589</v>
       </c>
       <c r="F55">
-        <v>-1.023655165256997</v>
+        <v>-1.419219652544025</v>
       </c>
       <c r="G55">
-        <v>-3.597914875619072</v>
+        <v>-4.924549075125742</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>10.19378970196722</v>
       </c>
       <c r="E56">
-        <v>-23.01170482222905</v>
+        <v>-24.49532327810695</v>
       </c>
       <c r="F56">
-        <v>-0.5092746279168242</v>
+        <v>-0.8059983167018155</v>
       </c>
       <c r="G56">
-        <v>-2.846701837716727</v>
+        <v>-4.928629668921651</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>10.48725909803753</v>
       </c>
       <c r="E57">
-        <v>-24.13080837976072</v>
+        <v>-22.84925196125838</v>
       </c>
       <c r="F57">
-        <v>-1.324496668401304</v>
+        <v>-1.483998811810349</v>
       </c>
       <c r="G57">
-        <v>-2.104057263562415</v>
+        <v>-5.361188275755666</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>10.63702298645733</v>
       </c>
       <c r="E58">
-        <v>-22.68532471026739</v>
+        <v>-23.64816784491372</v>
       </c>
       <c r="F58">
-        <v>-1.187620552232325</v>
+        <v>-1.486335636253647</v>
       </c>
       <c r="G58">
-        <v>-4.546249573128835</v>
+        <v>-5.861020549213486</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.64599389101992</v>
       </c>
       <c r="E59">
-        <v>-22.21635239389041</v>
+        <v>-23.08568597555822</v>
       </c>
       <c r="F59">
-        <v>-0.2692866509169738</v>
+        <v>-1.086639252361455</v>
       </c>
       <c r="G59">
-        <v>-3.935867930704914</v>
+        <v>-5.939462981198075</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>10.5233773905558</v>
       </c>
       <c r="E60">
-        <v>-21.31779266412978</v>
+        <v>-21.9895579830755</v>
       </c>
       <c r="F60">
-        <v>-1.357433384704016</v>
+        <v>-1.209405786558549</v>
       </c>
       <c r="G60">
-        <v>-3.410988173639952</v>
+        <v>-6.461024481887732</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>10.28171700041939</v>
       </c>
       <c r="E61">
-        <v>-21.70448571095059</v>
+        <v>-20.69611507376149</v>
       </c>
       <c r="F61">
-        <v>-1.041798896480514</v>
+        <v>-2.078712763139212</v>
       </c>
       <c r="G61">
-        <v>-5.4829795109311</v>
+        <v>-6.711546311361781</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>9.942232518930599</v>
       </c>
       <c r="E62">
-        <v>-20.09345919126092</v>
+        <v>-20.15047447632817</v>
       </c>
       <c r="F62">
-        <v>-1.659941563062756</v>
+        <v>-1.378695919199073</v>
       </c>
       <c r="G62">
-        <v>-4.414010138099766</v>
+        <v>-7.49557379802983</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>9.525380232982634</v>
       </c>
       <c r="E63">
-        <v>-21.11445974408882</v>
+        <v>-20.0250225750504</v>
       </c>
       <c r="F63">
-        <v>-1.864878001780548</v>
+        <v>-2.196377382502465</v>
       </c>
       <c r="G63">
-        <v>-4.933660573748727</v>
+        <v>-7.682221150337701</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>9.053599190012068</v>
       </c>
       <c r="E64">
-        <v>-19.15031889113958</v>
+        <v>-19.40050418813593</v>
       </c>
       <c r="F64">
-        <v>-1.376173540457549</v>
+        <v>-2.141202314904199</v>
       </c>
       <c r="G64">
-        <v>-5.739028286704536</v>
+        <v>-7.245861299379026</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>8.553616738361738</v>
       </c>
       <c r="E65">
-        <v>-18.61148956027898</v>
+        <v>-19.77647779652736</v>
       </c>
       <c r="F65">
-        <v>-1.495369811148578</v>
+        <v>-2.405014966775965</v>
       </c>
       <c r="G65">
-        <v>-6.604790354286568</v>
+        <v>-7.990200246772971</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>8.045575129697383</v>
       </c>
       <c r="E66">
-        <v>-19.07109638511848</v>
+        <v>-19.00922599601251</v>
       </c>
       <c r="F66">
-        <v>-2.347404499013468</v>
+        <v>-2.194320546241314</v>
       </c>
       <c r="G66">
-        <v>-6.759020091006585</v>
+        <v>-8.62386189871585</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>7.550489684605484</v>
       </c>
       <c r="E67">
-        <v>-19.11214257264176</v>
+        <v>-18.29349062877083</v>
       </c>
       <c r="F67">
-        <v>-2.136944506453809</v>
+        <v>-2.531272241208458</v>
       </c>
       <c r="G67">
-        <v>-5.976762689171311</v>
+        <v>-7.912971811023248</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>7.090549274527699</v>
       </c>
       <c r="E68">
-        <v>-17.99057616079446</v>
+        <v>-18.45894626152935</v>
       </c>
       <c r="F68">
-        <v>-2.564078075461527</v>
+        <v>-2.455880038777467</v>
       </c>
       <c r="G68">
-        <v>-7.318614918899581</v>
+        <v>-9.122806519012691</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>6.678653763863174</v>
       </c>
       <c r="E69">
-        <v>-18.07849133811843</v>
+        <v>-17.71424224529699</v>
       </c>
       <c r="F69">
-        <v>-2.36961799928694</v>
+        <v>-3.140102401448427</v>
       </c>
       <c r="G69">
-        <v>-5.175527784903236</v>
+        <v>-8.852704105105294</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>6.327761091816744</v>
       </c>
       <c r="E70">
-        <v>-18.71747536007728</v>
+        <v>-17.73223810996748</v>
       </c>
       <c r="F70">
-        <v>-2.319862111237788</v>
+        <v>-2.734749096562517</v>
       </c>
       <c r="G70">
-        <v>-6.918735002112531</v>
+        <v>-8.380852486802729</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>6.050507430738215</v>
       </c>
       <c r="E71">
-        <v>-16.48160234977848</v>
+        <v>-17.60048578710994</v>
       </c>
       <c r="F71">
-        <v>-2.400698344239977</v>
+        <v>-3.04191849829681</v>
       </c>
       <c r="G71">
-        <v>-6.615410863283217</v>
+        <v>-8.789206880532532</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>5.84984055574953</v>
       </c>
       <c r="E72">
-        <v>-18.47411378928762</v>
+        <v>-18.36312336984291</v>
       </c>
       <c r="F72">
-        <v>-3.811914992058049</v>
+        <v>-3.093736192811531</v>
       </c>
       <c r="G72">
-        <v>-7.490451517142065</v>
+        <v>-8.415805135388554</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>5.727818551747416</v>
       </c>
       <c r="E73">
-        <v>-17.47616771252385</v>
+        <v>-18.12705899135098</v>
       </c>
       <c r="F73">
-        <v>-3.427638667368969</v>
+        <v>-3.207707950293103</v>
       </c>
       <c r="G73">
-        <v>-5.247764476994749</v>
+        <v>-8.414070295607759</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>5.686906327544406</v>
       </c>
       <c r="E74">
-        <v>-19.13453253489391</v>
+        <v>-19.00243549549641</v>
       </c>
       <c r="F74">
-        <v>-3.949480309906157</v>
+        <v>-3.318120213044847</v>
       </c>
       <c r="G74">
-        <v>-6.803491514371609</v>
+        <v>-8.13531065263623</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>5.721607923330059</v>
       </c>
       <c r="E75">
-        <v>-20.54365068602704</v>
+        <v>-18.10787530824159</v>
       </c>
       <c r="F75">
-        <v>-2.845366794430155</v>
+        <v>-2.995272301477767</v>
       </c>
       <c r="G75">
-        <v>-4.618287848631424</v>
+        <v>-8.595903434889618</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>5.824745415817878</v>
       </c>
       <c r="E76">
-        <v>-17.89617366738111</v>
+        <v>-18.74930557167076</v>
       </c>
       <c r="F76">
-        <v>-2.942629553029859</v>
+        <v>-3.966810584340125</v>
       </c>
       <c r="G76">
-        <v>-5.655635882975195</v>
+        <v>-7.493391215551659</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>5.993310524449869</v>
       </c>
       <c r="E77">
-        <v>-19.3551345076235</v>
+        <v>-19.63474115364493</v>
       </c>
       <c r="F77">
-        <v>-3.051042136871244</v>
+        <v>-3.828947882594412</v>
       </c>
       <c r="G77">
-        <v>-5.722241198983677</v>
+        <v>-6.821884210016002</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>6.219603066969519</v>
       </c>
       <c r="E78">
-        <v>-18.75765767964499</v>
+        <v>-19.52040739908373</v>
       </c>
       <c r="F78">
-        <v>-3.335259134608768</v>
+        <v>-3.71812474961088</v>
       </c>
       <c r="G78">
-        <v>-5.091981347243019</v>
+        <v>-7.363214268749569</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>6.493878564685986</v>
       </c>
       <c r="E79">
-        <v>-20.46563261129013</v>
+        <v>-19.48619739740112</v>
       </c>
       <c r="F79">
-        <v>-3.974101045852164</v>
+        <v>-3.644154025643093</v>
       </c>
       <c r="G79">
-        <v>-4.376801806187219</v>
+        <v>-7.344659706940527</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>6.813536577865786</v>
       </c>
       <c r="E80">
-        <v>-19.72538914402064</v>
+        <v>-20.84777373849893</v>
       </c>
       <c r="F80">
-        <v>-2.399527032732419</v>
+        <v>-4.165372735893375</v>
       </c>
       <c r="G80">
-        <v>-5.055342157651335</v>
+        <v>-6.656394331874513</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>7.171613871103197</v>
       </c>
       <c r="E81">
-        <v>-23.33265253377782</v>
+        <v>-20.73162503058878</v>
       </c>
       <c r="F81">
-        <v>-3.02942257602558</v>
+        <v>-3.975483591047436</v>
       </c>
       <c r="G81">
-        <v>-3.049470537874722</v>
+        <v>-6.329463840452352</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>7.556715144907257</v>
       </c>
       <c r="E82">
-        <v>-22.08651054824229</v>
+        <v>-20.98223395514026</v>
       </c>
       <c r="F82">
-        <v>-3.704756556464502</v>
+        <v>-3.862673204664588</v>
       </c>
       <c r="G82">
-        <v>-3.808910031983666</v>
+        <v>-6.072164518019773</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>7.9671782469901</v>
       </c>
       <c r="E83">
-        <v>-22.78029204042092</v>
+        <v>-23.52125401324961</v>
       </c>
       <c r="F83">
-        <v>-3.191043683250986</v>
+        <v>-3.905534590820241</v>
       </c>
       <c r="G83">
-        <v>-3.201392376376195</v>
+        <v>-5.59952837096758</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>8.396964225193571</v>
       </c>
       <c r="E84">
-        <v>-23.78184725782598</v>
+        <v>-23.30525795187925</v>
       </c>
       <c r="F84">
-        <v>-3.954123309198848</v>
+        <v>-4.033109797790587</v>
       </c>
       <c r="G84">
-        <v>-2.81190844455096</v>
+        <v>-5.440682837810474</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>8.834016067881706</v>
       </c>
       <c r="E85">
-        <v>-26.64848923808311</v>
+        <v>-24.7901223711546</v>
       </c>
       <c r="F85">
-        <v>-3.1822596753117</v>
+        <v>-3.837265519685922</v>
       </c>
       <c r="G85">
-        <v>-2.408263834063526</v>
+        <v>-6.148633227093481</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>9.275724187516772</v>
       </c>
       <c r="E86">
-        <v>-25.8988927389101</v>
+        <v>-25.99909726854424</v>
       </c>
       <c r="F86">
-        <v>-2.567849632246473</v>
+        <v>-4.062188807098461</v>
       </c>
       <c r="G86">
-        <v>-2.341987471873524</v>
+        <v>-5.236470395893592</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>9.711342516779194</v>
       </c>
       <c r="E87">
-        <v>-26.40131501929726</v>
+        <v>-27.99986529216714</v>
       </c>
       <c r="F87">
-        <v>-3.865963479988508</v>
+        <v>-3.970649238884699</v>
       </c>
       <c r="G87">
-        <v>-2.955066013460065</v>
+        <v>-5.135165673524623</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>10.12379531969583</v>
       </c>
       <c r="E88">
-        <v>-28.19913637153242</v>
+        <v>-28.54471470284309</v>
       </c>
       <c r="F88">
-        <v>-3.70835995466668</v>
+        <v>-4.077874772237872</v>
       </c>
       <c r="G88">
-        <v>-2.066300675285734</v>
+        <v>-5.556375373621067</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>10.50470446883482</v>
       </c>
       <c r="E89">
-        <v>-30.04152791109997</v>
+        <v>-30.54587935814751</v>
       </c>
       <c r="F89">
-        <v>-4.022616039531923</v>
+        <v>-3.524689363913557</v>
       </c>
       <c r="G89">
-        <v>-3.525174309821474</v>
+        <v>-5.201126135619101</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>10.83679301537336</v>
       </c>
       <c r="E90">
-        <v>-33.33426860722788</v>
+        <v>-32.38810061605075</v>
       </c>
       <c r="F90">
-        <v>-3.121929677365812</v>
+        <v>-4.086890723049942</v>
       </c>
       <c r="G90">
-        <v>-2.942565768357815</v>
+        <v>-5.351510245556408</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>11.10051620374162</v>
       </c>
       <c r="E91">
-        <v>-34.38104191293201</v>
+        <v>-32.83710429237796</v>
       </c>
       <c r="F91">
-        <v>-3.702407306510163</v>
+        <v>-3.85406315387989</v>
       </c>
       <c r="G91">
-        <v>-3.816906742666246</v>
+        <v>-6.107138052562327</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>11.28408629515572</v>
       </c>
       <c r="E92">
-        <v>-33.55372429363182</v>
+        <v>-34.9691823218523</v>
       </c>
       <c r="F92">
-        <v>-3.496370795881452</v>
+        <v>-4.089026254214359</v>
       </c>
       <c r="G92">
-        <v>-4.147518383961876</v>
+        <v>-5.986858438505147</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>11.36810139784135</v>
       </c>
       <c r="E93">
-        <v>-36.01928027322195</v>
+        <v>-37.02112206220842</v>
       </c>
       <c r="F93">
-        <v>-3.006063443634036</v>
+        <v>-3.427518554095563</v>
       </c>
       <c r="G93">
-        <v>-3.896785084175948</v>
+        <v>-6.434572417690573</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>11.33731107628202</v>
       </c>
       <c r="E94">
-        <v>-38.06022438659559</v>
+        <v>-37.76930646953098</v>
       </c>
       <c r="F94">
-        <v>-3.092136615356725</v>
+        <v>-3.269541435075072</v>
       </c>
       <c r="G94">
-        <v>-3.860725479883491</v>
+        <v>-6.757887027854042</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>11.18858760927114</v>
       </c>
       <c r="E95">
-        <v>-40.14743112091648</v>
+        <v>-42.18146221403993</v>
       </c>
       <c r="F95">
-        <v>-3.370111864714155</v>
+        <v>-3.133646105911008</v>
       </c>
       <c r="G95">
-        <v>-6.088432067567</v>
+        <v>-7.131090356409095</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>10.90456625778293</v>
       </c>
       <c r="E96">
-        <v>-45.10571754179508</v>
+        <v>-43.61647979099469</v>
       </c>
       <c r="F96">
-        <v>-2.341376469423297</v>
+        <v>-2.902446278687457</v>
       </c>
       <c r="G96">
-        <v>-4.303933313904656</v>
+        <v>-6.640737696561606</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>10.49663485322026</v>
       </c>
       <c r="E97">
-        <v>-45.70466252997692</v>
+        <v>-45.2422834365781</v>
       </c>
       <c r="F97">
-        <v>-2.536717100147059</v>
+        <v>-2.576270815263332</v>
       </c>
       <c r="G97">
-        <v>-5.718849841759821</v>
+        <v>-8.060960562798209</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>9.950092976034394</v>
       </c>
       <c r="E98">
-        <v>-47.60409738878816</v>
+        <v>-46.90056934793299</v>
       </c>
       <c r="F98">
-        <v>-1.737086590918071</v>
+        <v>-2.594035154216368</v>
       </c>
       <c r="G98">
-        <v>-6.037042171035526</v>
+        <v>-8.091888748596833</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>9.301071539524584</v>
       </c>
       <c r="E99">
-        <v>-48.86183929355393</v>
+        <v>-50.70715469389417</v>
       </c>
       <c r="F99">
-        <v>-1.440920393395164</v>
+        <v>-2.186024446702277</v>
       </c>
       <c r="G99">
-        <v>-7.605342554363188</v>
+        <v>-8.317429668450814</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>8.50997918286278</v>
       </c>
       <c r="E100">
-        <v>-49.9688850403068</v>
+        <v>-51.80763213693682</v>
       </c>
       <c r="F100">
-        <v>-1.534339527245878</v>
+        <v>-1.707173415635578</v>
       </c>
       <c r="G100">
-        <v>-6.836337292072405</v>
+        <v>-9.597835413482642</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>7.679286453116259</v>
       </c>
       <c r="E101">
-        <v>-53.10200848049607</v>
+        <v>-55.62982525105671</v>
       </c>
       <c r="F101">
-        <v>-0.4251050444857692</v>
+        <v>-1.415810920681505</v>
       </c>
       <c r="G101">
-        <v>-7.894195335923962</v>
+        <v>-9.413659130930258</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>6.677522692605146</v>
       </c>
       <c r="E102">
-        <v>-55.82734211778865</v>
+        <v>-56.77559034868812</v>
       </c>
       <c r="F102">
-        <v>-0.6073425596320493</v>
+        <v>-1.015644024104523</v>
       </c>
       <c r="G102">
-        <v>-7.619721230198745</v>
+        <v>-9.685884080190233</v>
       </c>
     </row>
   </sheetData>
